--- a/data/trans_dic/P44A$analisis-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 67,46</t>
+          <t>19,53; 68,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 46,88</t>
+          <t>13,38; 47,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,68</t>
+          <t>2,52; 11,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 48,51</t>
+          <t>6,64; 49,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 40,7</t>
+          <t>8,03; 40,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,74</t>
+          <t>5,96; 14,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 48,14</t>
+          <t>16,36; 50,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 38,72</t>
+          <t>13,89; 38,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,41</t>
+          <t>5,26; 11,53</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,01; 67,56</t>
+          <t>24,58; 69,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 59,31</t>
+          <t>29,37; 59,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 91,8</t>
+          <t>11,18; 91,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 52,25</t>
+          <t>20,38; 51,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,6; 58,72</t>
+          <t>20,45; 56,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 17,54</t>
+          <t>8,95; 18,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 52,36</t>
+          <t>27,39; 52,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,23; 55,16</t>
+          <t>30,54; 54,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 85,78</t>
+          <t>11,89; 84,16</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 56,74</t>
+          <t>18,15; 58,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 40,63</t>
+          <t>9,47; 41,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,19; 33,48</t>
+          <t>16,92; 32,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 53,58</t>
+          <t>15,57; 54,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 54,24</t>
+          <t>11,24; 55,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,68; 23,69</t>
+          <t>10,36; 23,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 48,9</t>
+          <t>22,72; 49,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 39,01</t>
+          <t>14,45; 39,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 26,59</t>
+          <t>16,09; 26,59</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 50,11</t>
+          <t>19,1; 49,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,48; 57,61</t>
+          <t>30,78; 55,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,89</t>
+          <t>7,75; 15,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 53,4</t>
+          <t>15,11; 52,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,18; 58,11</t>
+          <t>24,03; 59,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,35</t>
+          <t>6,4; 12,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,29; 45,32</t>
+          <t>20,61; 44,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,57; 53,59</t>
+          <t>32,22; 52,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,02</t>
+          <t>7,93; 13,09</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 47,61</t>
+          <t>27,93; 49,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,1; 44,33</t>
+          <t>29,47; 44,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 74,31</t>
+          <t>12,46; 74,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 41,96</t>
+          <t>22,85; 42,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,43; 44,45</t>
+          <t>24,92; 44,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,41</t>
+          <t>9,3; 13,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,24; 41,87</t>
+          <t>27,99; 42,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 41,98</t>
+          <t>29,07; 41,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 60,49</t>
+          <t>11,86; 62,71</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2913; 10254</t>
+          <t>2968; 10428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3846; 14480</t>
+          <t>4134; 14742</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2341; 10737</t>
+          <t>2319; 10715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1010; 7374</t>
+          <t>1009; 7495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1895; 10405</t>
+          <t>2052; 10475</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6154; 14375</t>
+          <t>5808; 14130</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5030; 14636</t>
+          <t>4975; 15306</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7757; 21857</t>
+          <t>7843; 21813</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10034; 21618</t>
+          <t>9960; 21830</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6335; 17823</t>
+          <t>6485; 18337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11553; 23431</t>
+          <t>11601; 23557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44087; 355243</t>
+          <t>43272; 353332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7365; 19002</t>
+          <t>7413; 18897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7273; 19775</t>
+          <t>6887; 19065</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10991; 22303</t>
+          <t>11379; 23097</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16961; 32854</t>
+          <t>17190; 32835</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22123; 40368</t>
+          <t>22349; 39872</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60766; 441052</t>
+          <t>61145; 432740</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4263; 14954</t>
+          <t>4783; 15299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2973; 12510</t>
+          <t>2914; 12747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18330; 35713</t>
+          <t>18049; 34662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4290; 14157</t>
+          <t>4114; 14405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2369; 11011</t>
+          <t>2282; 11213</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7722; 17130</t>
+          <t>7489; 17025</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11863; 25807</t>
+          <t>11988; 25933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7590; 19929</t>
+          <t>7385; 20124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28258; 47583</t>
+          <t>28788; 47591</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7813; 20762</t>
+          <t>7914; 20420</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17831; 33705</t>
+          <t>18007; 32390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14429; 30389</t>
+          <t>14820; 30572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4429; 15465</t>
+          <t>4377; 15064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8845; 21261</t>
+          <t>8793; 21655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10794; 22366</t>
+          <t>11601; 23136</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14985; 31902</t>
+          <t>14509; 31099</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30969; 50960</t>
+          <t>30642; 49897</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29113; 48491</t>
+          <t>29513; 48725</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30607; 52072</t>
+          <t>30546; 53643</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46469; 70793</t>
+          <t>47067; 71353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100031; 577175</t>
+          <t>96806; 574811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25357; 44873</t>
+          <t>24440; 45004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29533; 51612</t>
+          <t>28939; 51378</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44190; 64092</t>
+          <t>44454; 64367</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61085; 90565</t>
+          <t>60545; 90964</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82559; 115787</t>
+          <t>80188; 113112</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>149064; 759094</t>
+          <t>148812; 786892</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$analisis-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 68,6</t>
+          <t>19,65; 66,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,38; 47,73</t>
+          <t>13,38; 46,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,66</t>
+          <t>2,8; 11,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 49,31</t>
+          <t>6,67; 48,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 40,98</t>
+          <t>7,6; 41,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 14,49</t>
+          <t>6,18; 14,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 50,35</t>
+          <t>15,94; 49,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 38,64</t>
+          <t>13,99; 38,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,53</t>
+          <t>5,16; 11,82</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 69,51</t>
+          <t>25,65; 68,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,37; 59,63</t>
+          <t>29,5; 60,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 91,3</t>
+          <t>8,89; 19,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,38; 51,96</t>
+          <t>20,92; 52,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,45; 56,62</t>
+          <t>20,83; 60,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 18,16</t>
+          <t>8,95; 18,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 52,33</t>
+          <t>25,55; 52,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,54; 54,49</t>
+          <t>30,6; 55,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,89; 84,16</t>
+          <t>9,93; 17,04</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 58,05</t>
+          <t>18,37; 58,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 41,4</t>
+          <t>10,06; 42,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,92; 32,5</t>
+          <t>16,28; 31,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 54,52</t>
+          <t>16,49; 54,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 55,23</t>
+          <t>10,53; 51,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 23,55</t>
+          <t>12,09; 25,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 49,14</t>
+          <t>21,79; 50,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,45; 39,39</t>
+          <t>14,29; 39,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,09; 26,59</t>
+          <t>16,09; 26,24</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 49,29</t>
+          <t>19,79; 46,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 55,36</t>
+          <t>30,87; 56,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,99</t>
+          <t>7,56; 15,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 52,01</t>
+          <t>14,44; 52,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 59,19</t>
+          <t>24,64; 60,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,77</t>
+          <t>6,41; 13,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 44,18</t>
+          <t>21,51; 45,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 52,47</t>
+          <t>32,47; 53,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,09</t>
+          <t>7,77; 12,84</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,93; 49,05</t>
+          <t>28,55; 47,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,47; 44,68</t>
+          <t>29,02; 44,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 74,0</t>
+          <t>10,82; 16,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 42,08</t>
+          <t>22,73; 42,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,92; 44,24</t>
+          <t>25,02; 43,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,46</t>
+          <t>9,68; 13,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 42,05</t>
+          <t>27,88; 41,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 41,01</t>
+          <t>29,82; 41,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 62,71</t>
+          <t>10,92; 14,19</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>16895</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2968; 10428</t>
+          <t>2987; 10170</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4134; 14742</t>
+          <t>4133; 14488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2319; 10715</t>
+          <t>2819; 11880</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1009; 7495</t>
+          <t>1014; 7324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2052; 10475</t>
+          <t>1943; 10536</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5808; 14130</t>
+          <t>6543; 15229</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4975; 15306</t>
+          <t>4845; 15027</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7843; 21813</t>
+          <t>7897; 21515</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9960; 21830</t>
+          <t>10657; 24432</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263147</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>279594</t>
+          <t>38912</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6485; 18337</t>
+          <t>6767; 18089</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11601; 23557</t>
+          <t>11653; 23747</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43272; 353332</t>
+          <t>13680; 29457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7413; 18897</t>
+          <t>7607; 19162</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6887; 19065</t>
+          <t>7014; 20522</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11379; 23097</t>
+          <t>12553; 25612</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17190; 32835</t>
+          <t>16032; 32756</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22349; 39872</t>
+          <t>22394; 40388</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61145; 432740</t>
+          <t>29222; 50137</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>42387</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4783; 15299</t>
+          <t>4840; 15310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2914; 12747</t>
+          <t>3096; 12952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18049; 34662</t>
+          <t>19216; 37173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4114; 14405</t>
+          <t>4356; 14285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2282; 11213</t>
+          <t>2138; 10516</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7489; 17025</t>
+          <t>10285; 21438</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11988; 25933</t>
+          <t>11499; 26882</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7385; 20124</t>
+          <t>7302; 20094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28788; 47591</t>
+          <t>32688; 53311</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38024</t>
+          <t>40031</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7914; 20420</t>
+          <t>8200; 19382</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18007; 32390</t>
+          <t>18062; 33062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14820; 30572</t>
+          <t>14967; 31512</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4377; 15064</t>
+          <t>4181; 15104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8793; 21655</t>
+          <t>9014; 22207</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11601; 23136</t>
+          <t>12619; 25713</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14509; 31099</t>
+          <t>15139; 31745</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30642; 49897</t>
+          <t>30872; 50630</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29513; 48725</t>
+          <t>30677; 50726</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30546; 53643</t>
+          <t>31229; 52413</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47067; 71353</t>
+          <t>46341; 70995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96806; 574811</t>
+          <t>61756; 94022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24440; 45004</t>
+          <t>24308; 45114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28939; 51378</t>
+          <t>29060; 50732</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44454; 64367</t>
+          <t>51114; 73872</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60545; 90964</t>
+          <t>60319; 89254</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80188; 113112</t>
+          <t>82236; 114733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>148812; 786892</t>
+          <t>120008; 155990</t>
         </is>
       </c>
     </row>
